--- a/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 17,04</t>
+          <t>5,1; 16,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 17,76</t>
+          <t>5,8; 16,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 15,33</t>
+          <t>6,43; 15,03</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 15,82</t>
+          <t>6,66; 16,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,54</t>
+          <t>8,81; 17,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 14,65</t>
+          <t>8,64; 14,7</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 17,87</t>
+          <t>7,12; 17,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,79</t>
+          <t>5,04; 12,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,23</t>
+          <t>6,87; 13,3</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,64</t>
+          <t>5,65; 11,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,16</t>
+          <t>5,93; 12,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,95</t>
+          <t>6,53; 11,19</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,4</t>
+          <t>7,72; 12,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,81</t>
+          <t>7,82; 11,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,28</t>
+          <t>8,24; 11,26</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5671</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12015</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2932; 9621</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3563; 10431</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7644; 17878</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16445</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22669</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39114</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10609; 25576</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16086; 31645</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29533; 50242</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>19776</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17792</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37568</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12386; 30839</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10661; 27033</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26465; 51258</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22914</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26524</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49438</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15510; 32720</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18125; 37576</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37892; 64877</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>64805</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73329</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138135</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>51383; 83388</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59503; 88982</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>117506; 160601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 16,73</t>
+          <t>5,08; 16,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 16,98</t>
+          <t>6,17; 17,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 15,03</t>
+          <t>6,7; 14,84</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 16,06</t>
+          <t>6,83; 16,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 17,33</t>
+          <t>8,79; 16,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 14,7</t>
+          <t>8,6; 14,96</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 17,74</t>
+          <t>7,05; 18,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,78</t>
+          <t>5,39; 12,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 13,3</t>
+          <t>7,12; 13,35</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,92</t>
+          <t>5,4; 11,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 12,3</t>
+          <t>5,99; 12,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,19</t>
+          <t>6,51; 11,01</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,54</t>
+          <t>7,62; 12,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,69</t>
+          <t>7,63; 11,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,26</t>
+          <t>8,22; 11,2</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2932; 9621</t>
+          <t>2923; 9603</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3563; 10431</t>
+          <t>3789; 10450</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7644; 17878</t>
+          <t>7964; 17652</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10609; 25576</t>
+          <t>10887; 25486</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16086; 31645</t>
+          <t>16042; 30998</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29533; 50242</t>
+          <t>29410; 51144</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12386; 30839</t>
+          <t>12254; 31873</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10661; 27033</t>
+          <t>11401; 26195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26465; 51258</t>
+          <t>27434; 51462</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15510; 32720</t>
+          <t>14824; 32420</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18125; 37576</t>
+          <t>18285; 37663</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37892; 64877</t>
+          <t>37733; 63858</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51383; 83388</t>
+          <t>50689; 81698</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59503; 88982</t>
+          <t>58030; 90503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117506; 160601</t>
+          <t>117272; 159766</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 16,7</t>
+          <t>6,5; 18,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 17,01</t>
+          <t>4,86; 17,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,84</t>
+          <t>7,34; 16,14</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,0</t>
+          <t>8,52; 17,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,98</t>
+          <t>6,35; 13,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 14,96</t>
+          <t>8,38; 13,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 18,33</t>
+          <t>5,68; 13,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,38</t>
+          <t>6,93; 14,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 13,35</t>
+          <t>7,05; 12,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,81</t>
+          <t>6,22; 12,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,33</t>
+          <t>6,77; 13,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,01</t>
+          <t>7,2; 11,86</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,28</t>
+          <t>7,84; 11,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,89</t>
+          <t>7,92; 12,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,2</t>
+          <t>8,45; 11,21</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>10986</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2923; 9603</t>
+          <t>3286; 9322</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3789; 10450</t>
+          <t>2532; 9236</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7964; 17652</t>
+          <t>7537; 16568</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>32708</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10887; 25486</t>
+          <t>13429; 27075</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16042; 30998</t>
+          <t>9246; 19844</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29410; 51144</t>
+          <t>25400; 41663</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>35477</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12254; 31873</t>
+          <t>11305; 27010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11401; 26195</t>
+          <t>12167; 25545</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27434; 51462</t>
+          <t>26412; 47732</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49438</t>
+          <t>50368</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14824; 32420</t>
+          <t>18211; 36219</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18285; 37663</t>
+          <t>17308; 34146</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37733; 63858</t>
+          <t>39444; 64990</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129540</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50689; 81698</t>
+          <t>54905; 83074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58030; 90503</t>
+          <t>49795; 75604</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117272; 159766</t>
+          <t>112229; 148939</t>
         </is>
       </c>
     </row>
